--- a/산출물/통합기능테스트명세서.xlsx
+++ b/산출물/통합기능테스트명세서.xlsx
@@ -119,8 +119,9 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -166,6 +167,11 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Y/N</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
@@ -193,8 +199,9 @@
 잘못된 입력도 명확한 오류로 차단됨</t>
         </is>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -218,8 +225,9 @@
 틀린 자격은 401</t>
         </is>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -243,8 +251,9 @@
 만료·무효 토큰은 401</t>
         </is>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -268,8 +277,9 @@
 만료 시 재로그인 유도(401)</t>
         </is>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -292,8 +302,9 @@
           <t xml:space="preserve">로그아웃 후 해당 refresh 토큰 재사용 불가</t>
         </is>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -312,8 +323,9 @@
         </is>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -340,8 +352,9 @@
           <t xml:space="preserve">생성되고 생성자가 자동 OWNER 멤버로 등록됨</t>
         </is>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -364,8 +377,9 @@
           <t xml:space="preserve">내가 멤버인 프로젝트만 표시됨</t>
         </is>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -388,8 +402,9 @@
           <t xml:space="preserve">나에게 온 초대의 프로젝트·초대자·역할·상태가 표시되고 남의 초대는 안 보임</t>
         </is>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -412,8 +427,9 @@
           <t xml:space="preserve">수락한 사용자가 해당 프로젝트 멤버가 됨</t>
         </is>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -436,8 +452,9 @@
           <t xml:space="preserve">거절 상태가 이력으로 보존되고 멤버로 등록되지 않음</t>
         </is>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -461,8 +478,9 @@
 VIEWER는 403</t>
         </is>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -485,8 +503,9 @@
           <t xml:space="preserve">보관 상태가 목록에서 구분 표시되고 문서는 유지됨</t>
         </is>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -510,8 +529,9 @@
 비OWNER는 차단됨</t>
         </is>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -535,8 +555,9 @@
 이미 멤버면 409</t>
         </is>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -560,8 +581,9 @@
 취소 후 재사용되지 않음</t>
         </is>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -584,8 +606,9 @@
           <t xml:space="preserve">역할 변경이 즉시 반영되고 역할별 허용 동작이 표와 일치함</t>
         </is>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">금액 열람은 AMT-003-1 정책 미결이라 그 항목만 제외</t>
         </is>
@@ -612,8 +635,9 @@
           <t xml:space="preserve">제외 즉시 프로젝트 범위 밖 데이터 접근이 차단됨</t>
         </is>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -636,8 +660,9 @@
           <t xml:space="preserve">최근 초대 이력이 선택 목록에 노출됨</t>
         </is>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -662,8 +687,9 @@
 열린 태스크·금액 승인대기 카드에서도 이동 가능</t>
         </is>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-25 feat/dashboard-amount-link 로 금액 승인대기 이동 확인됨 — PR 머지 여부 확인</t>
         </is>
@@ -686,8 +712,9 @@
         </is>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -716,8 +743,9 @@
 내부 저장명 충돌·경로 조작 없음</t>
         </is>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -740,8 +768,9 @@
           <t xml:space="preserve">전략(AUTO·TEXT_ONLY·TEXT_WITH_IMAGE_OCR)과 실제 추출 방법이 기록됨</t>
         </is>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -760,8 +789,9 @@
         </is>
       </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E28" s="4"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P0, 미구현</t>
         </is>
@@ -789,8 +819,9 @@
 단계별 상태를 지속 확인 가능함</t>
         </is>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">선행 DOC-003-1 미구현이라 모드 연동은 확인 불가</t>
         </is>
@@ -819,8 +850,9 @@
 쿼리 수가 문서 수와 무관함</t>
         </is>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E30" s="4"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">⚠ 알려진 미달 — N+1 3곳으로 문서 20건에 약 62쿼리(명세서 근거). 3번 절차는 실패가 예상됨</t>
         </is>
@@ -847,8 +879,9 @@
           <t xml:space="preserve">9종 문서 유형과 유형 출처(사용자/AI/AI수정)가 저장됨</t>
         </is>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -871,8 +904,9 @@
           <t xml:space="preserve">메타정보가 정확히 표시되고 본문 검색·복사가 정상 동작함</t>
         </is>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -895,8 +929,9 @@
           <t xml:space="preserve">업로드 당시 파일명으로 각각 정상 다운로드됨</t>
         </is>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -919,8 +954,9 @@
           <t xml:space="preserve">하위 데이터가 함께 정리됨(cascade)</t>
         </is>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -943,8 +979,9 @@
           <t xml:space="preserve">기존 이력을 덮지 않고 새 행으로 쌓임</t>
         </is>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -963,8 +1000,9 @@
         </is>
       </c>
       <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="E36" s="4"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -987,8 +1025,9 @@
         </is>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E37" s="4"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1011,8 +1050,9 @@
         </is>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E38" s="4"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1035,8 +1075,9 @@
         </is>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="E39" s="4"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1059,8 +1100,9 @@
         </is>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E40" s="4"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1083,8 +1125,9 @@
         </is>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="E41" s="4"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1107,8 +1150,9 @@
         </is>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="E42" s="4"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현·범위 밖 가능성</t>
         </is>
@@ -1136,8 +1180,9 @@
 신뢰도 구간이 시각적으로 구분됨</t>
         </is>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E43" s="4"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">신뢰도 구간 시각 구분은 명세서에 「미확인」으로 남아 있음 — 3번 절차 결과를 특히 확인</t>
         </is>
@@ -1160,8 +1205,9 @@
         </is>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E44" s="4"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1188,8 +1234,9 @@
           <t xml:space="preserve">text만 바뀌고 original_text는 보존됨</t>
         </is>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="4"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1208,8 +1255,9 @@
         </is>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="E46" s="4"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1232,8 +1280,9 @@
         </is>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="E47" s="4"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1256,8 +1305,9 @@
         </is>
       </c>
       <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="E48" s="4"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1280,8 +1330,9 @@
         </is>
       </c>
       <c r="D49" s="4"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E49" s="4"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1304,8 +1355,9 @@
         </is>
       </c>
       <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="E50" s="4"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1328,8 +1380,9 @@
         </is>
       </c>
       <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E51" s="4"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1352,8 +1405,9 @@
         </is>
       </c>
       <c r="D52" s="4"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="E52" s="4"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -1381,8 +1435,9 @@
 텍스트가 같은 트랜잭션에서 갱신됨</t>
         </is>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="4"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -1406,8 +1461,9 @@
 되돌리기가 가능함</t>
         </is>
       </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="E54" s="4"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">되돌리기는 명세서에 「미확인」으로 남아 있음 — 2번 절차 결과를 특히 확인</t>
         </is>
@@ -1435,8 +1491,9 @@
 복원 시 다시 포함됨</t>
         </is>
       </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="4"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -1459,8 +1516,9 @@
           <t xml:space="preserve">나중 요청이 409를 받음</t>
         </is>
       </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="4"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -1479,8 +1537,9 @@
         </is>
       </c>
       <c r="D57" s="4"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="E57" s="4"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1507,8 +1566,9 @@
           <t xml:space="preserve">요약문과 토큰·지연시간이 함께 기록됨</t>
         </is>
       </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="4"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -1532,8 +1592,9 @@
 사용자 지정 유형은 자동 분류로 덮지 않음</t>
         </is>
       </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="4"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -1552,8 +1613,9 @@
         </is>
       </c>
       <c r="D60" s="4"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="E60" s="4"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1576,8 +1638,9 @@
         </is>
       </c>
       <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="E61" s="4"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현. DLV-003-1·DLV-003-2 의 재료</t>
         </is>
@@ -1600,8 +1663,9 @@
         </is>
       </c>
       <c r="D62" s="4"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="E62" s="4"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1628,8 +1692,9 @@
           <t xml:space="preserve">분석기별 진행 상태가 표시됨</t>
         </is>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="4"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -1653,8 +1718,9 @@
 어느 OCR 리비전으로 분석했는지 함께 기록됨</t>
         </is>
       </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="4"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -1673,8 +1739,9 @@
         </is>
       </c>
       <c r="D65" s="4"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="E65" s="4"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1697,8 +1764,9 @@
         </is>
       </c>
       <c r="D66" s="4"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="E66" s="4"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1721,8 +1789,9 @@
         </is>
       </c>
       <c r="D67" s="4"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="4"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -1745,8 +1814,9 @@
         </is>
       </c>
       <c r="D68" s="4"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="E68" s="4"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -1773,8 +1843,9 @@
           <t xml:space="preserve">사람이 태스크를 직접 만들고 수정·삭제할 수 있음</t>
         </is>
       </c>
-      <c r="E69" s="5"/>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="E69" s="4"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">명세서 표기는 미구현이나 관리/명세서_갱신목록_0824.md 기준 PR #50 으로 화면까지 구현 확인됨(최재정 담당) — 실제 동작 확인 필요</t>
         </is>
@@ -1801,8 +1872,9 @@
           <t xml:space="preserve">드래그로 상태가 바뀌고 완료 시 completed_at 이 정확히 기록됨</t>
         </is>
       </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="E70" s="4"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PR #50 로 구현 확인됨 — 실제 동작 확인 필요</t>
         </is>
@@ -1825,8 +1897,9 @@
         </is>
       </c>
       <c r="D71" s="4"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="E71" s="4"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 선행(ANL-002-1) 미구현</t>
         </is>
@@ -1849,8 +1922,9 @@
         </is>
       </c>
       <c r="D72" s="4"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="E72" s="4"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1873,8 +1947,9 @@
         </is>
       </c>
       <c r="D73" s="4"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="E73" s="4"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1897,8 +1972,9 @@
         </is>
       </c>
       <c r="D74" s="4"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="E74" s="4"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -1921,8 +1997,9 @@
         </is>
       </c>
       <c r="D75" s="4"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E75" s="4"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1945,8 +2022,9 @@
         </is>
       </c>
       <c r="D76" s="4"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="E76" s="4"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -1973,8 +2051,9 @@
           <t xml:space="preserve">주요 변경이 활동 이력에 남음</t>
         </is>
       </c>
-      <c r="E77" s="5"/>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="E77" s="4"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">리비전 0020 + PR #50 로 구현 확인됨(최재정, 김보현) — 실제 동작 확인 필요</t>
         </is>
@@ -1997,8 +2076,9 @@
         </is>
       </c>
       <c r="D78" s="4"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="E78" s="4"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -2021,8 +2101,9 @@
         </is>
       </c>
       <c r="D79" s="4"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="E79" s="4"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현. 추출이 없어 승인 대기 항목이 생기지 않음</t>
         </is>
@@ -2052,8 +2133,9 @@
 수정 후 decision이 EDITED가 되고 응답에 재검산 결과가 함께 옴</t>
         </is>
       </c>
-      <c r="E80" s="5"/>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="E80" s="4"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">추출(AMT-001-1)이 없어 승인 대기 항목이 안 생김 — 「승인」 흐름은 확인 불가, 「수정」만 확인</t>
         </is>
@@ -2081,8 +2163,9 @@
 불일치 금액이 "문서 금액이 N원 많음/적음" 형태로 표시됨(부호 그대로 노출 금지)</t>
         </is>
       </c>
-      <c r="E81" s="5"/>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="E81" s="4"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-25 실제 데이터로 확인됨(패치44) — 회귀 확인 목적</t>
         </is>
@@ -2110,8 +2193,9 @@
 부가세가 항목 합계에 섞이지 않음</t>
         </is>
       </c>
-      <c r="E82" s="5"/>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="E82" s="4"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-25 확인됨 — 회귀 확인 목적</t>
         </is>
@@ -2134,8 +2218,9 @@
         </is>
       </c>
       <c r="D83" s="4"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="E83" s="4"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, VIEWER 노출 정책 미결</t>
         </is>
@@ -2163,8 +2248,9 @@
 계약금액·집행률·잔액은 아직 없음</t>
         </is>
       </c>
-      <c r="E84" s="5"/>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="E84" s="4"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">계약금액을 담는 컬럼이 없어 2번 절차는 실패가 예상됨(부분 구현)</t>
         </is>
@@ -2192,8 +2278,9 @@
 원문 위치 이동은 아직 없음</t>
         </is>
       </c>
-      <c r="E85" s="5"/>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="E85" s="4"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">amount_items 에 위치 컬럼이 없어 2번 절차는 실패가 예상됨(부분 구현)</t>
         </is>
@@ -2216,8 +2303,9 @@
         </is>
       </c>
       <c r="D86" s="4"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="E86" s="4"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -2240,8 +2328,9 @@
         </is>
       </c>
       <c r="D87" s="4"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="E87" s="4"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -2269,8 +2358,9 @@
 어긋나지 않은 항목 강제 호출은 409</t>
         </is>
       </c>
-      <c r="E88" s="5"/>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="E88" s="4"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-25 패치47로 확인됨 — 회귀 확인 목적. 최종 승인은 TSK-002-1 미구현으로 확인 불가</t>
         </is>
@@ -2297,8 +2387,9 @@
           <t xml:space="preserve">형식을 고르지 않으면 생성 버튼이 비활성화됨</t>
         </is>
       </c>
-      <c r="E89" s="5"/>
-      <c r="F89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="4"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -2322,8 +2413,9 @@
 대상이 없으면 생성이 방지됨</t>
         </is>
       </c>
-      <c r="E90" s="5"/>
-      <c r="F90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="4"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -2348,8 +2440,9 @@
 이력에 쌓이지 않음</t>
         </is>
       </c>
-      <c r="E91" s="5"/>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="E91" s="4"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-25 신규 추가(명세에 없던 항목, PR #67)</t>
         </is>
@@ -2378,8 +2471,9 @@
 XLSX·PDF는 501</t>
         </is>
       </c>
-      <c r="E92" s="5"/>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="E92" s="4"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">개요(LLM 1회) 문장이 비어 있어 부분 구현 — 완료판정 미충족으로 기록될 것으로 예상</t>
         </is>
@@ -2406,8 +2500,9 @@
           <t xml:space="preserve">현재 상태가 한 페이지 요약으로 생성됨</t>
         </is>
       </c>
-      <c r="E93" s="5"/>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="E93" s="4"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">개요 자리가 비어 부분 구현으로 기록될 것으로 예상</t>
         </is>
@@ -2430,8 +2525,9 @@
         </is>
       </c>
       <c r="D94" s="4"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="E94" s="4"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -2458,8 +2554,9 @@
           <t xml:space="preserve">결정 상태별로 표가 정확히 생성됨</t>
         </is>
       </c>
-      <c r="E95" s="5"/>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="E95" s="4"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">결정 데이터 생성 경로(ANL-002-2)가 없어 실제 데이터로 검증 불가 — 데이터를 수동으로 넣고 확인</t>
         </is>
@@ -2486,8 +2583,9 @@
           <t xml:space="preserve">PENDING 상태 항목만 안건으로 생성됨</t>
         </is>
       </c>
-      <c r="E96" s="5"/>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="E96" s="4"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DLV-003-1 과 같은 이유로 실제 데이터 검증 필요</t>
         </is>
@@ -2515,8 +2613,9 @@
 파일이 없으면 410 DELIVERABLE_FILE_MISSING</t>
         </is>
       </c>
-      <c r="E97" s="5"/>
-      <c r="F97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="4"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -2539,8 +2638,9 @@
           <t xml:space="preserve">대상이 추가되면 갱신 필요 표시가 뜨고 늘어난 항목이 stale_changes에 표시됨</t>
         </is>
       </c>
-      <c r="E98" s="5"/>
-      <c r="F98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="4"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -2565,8 +2665,9 @@
 문서 열람 후 복귀해도 검색 결과가 유지됨</t>
         </is>
       </c>
-      <c r="E99" s="5"/>
-      <c r="F99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="4"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -2585,8 +2686,9 @@
         </is>
       </c>
       <c r="D100" s="4"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="E100" s="4"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현(박세현 담당)</t>
         </is>
@@ -2614,8 +2716,9 @@
 클릭 시 원문 해당 위치로 이동해 강조됨</t>
         </is>
       </c>
-      <c r="E101" s="5"/>
-      <c r="F101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="4"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -2638,8 +2741,9 @@
           <t xml:space="preserve">과거 사업의 단가가 출처와 함께 표시됨</t>
         </is>
       </c>
-      <c r="E102" s="5"/>
-      <c r="F102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="4"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -2662,8 +2766,9 @@
           <t xml:space="preserve">고유 문자열이 의미 검색에서 누락돼도 키워드 검색으로 찾힘</t>
         </is>
       </c>
-      <c r="E103" s="5"/>
-      <c r="F103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="4"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -2686,8 +2791,9 @@
           <t xml:space="preserve">두 방식 중 한쪽만 찾는 질의도 결합 결과에서 상위에 나옴</t>
         </is>
       </c>
-      <c r="E104" s="5"/>
-      <c r="F104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="4"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -2706,8 +2812,9 @@
         </is>
       </c>
       <c r="D105" s="4"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="E105" s="4"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
@@ -2734,8 +2841,9 @@
           <t xml:space="preserve">element_type으로 단락을 묶고 토큰 수 기준으로 자르며 표는 행 단위를 유지함</t>
         </is>
       </c>
-      <c r="E106" s="5"/>
-      <c r="F106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="4"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -2758,8 +2866,9 @@
           <t xml:space="preserve">청크마다 모델·차원·출처가 기록되고 프로젝트 범위 인덱스가 유지됨</t>
         </is>
       </c>
-      <c r="E107" s="5"/>
-      <c r="F107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="4"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -2784,8 +2893,9 @@
 본문이 비면 기존 청크가 삭제됨</t>
         </is>
       </c>
-      <c r="E108" s="5"/>
-      <c r="F108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="4"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -2808,8 +2918,9 @@
           <t xml:space="preserve">긴 문서에서도 컨텍스트 한도를 넘지 않음</t>
         </is>
       </c>
-      <c r="E109" s="5"/>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="E109" s="4"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">부르는 곳이 없어 부분 구현 — 단위 호출로만 확인 가능(연결된 화면 경로 없음)</t>
         </is>
@@ -2836,8 +2947,9 @@
           <t xml:space="preserve">같은 질의셋으로 청킹·임베딩 변경 효과를 비교할 수 있음</t>
         </is>
       </c>
-      <c r="E110" s="5"/>
-      <c r="F110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="4"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -2856,8 +2968,9 @@
         </is>
       </c>
       <c r="D111" s="4"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="E111" s="4"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 할지 말지 결정 전</t>
         </is>
@@ -2884,8 +2997,9 @@
           <t xml:space="preserve">401 반환</t>
         </is>
       </c>
-      <c r="E112" s="5"/>
-      <c r="F112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="4"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -2908,8 +3022,9 @@
           <t xml:space="preserve">404 반환</t>
         </is>
       </c>
-      <c r="E113" s="5"/>
-      <c r="F113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="4"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -2932,8 +3047,9 @@
           <t xml:space="preserve">create_all() 의존 없이 컬럼 추가가 데이터 유실 없이 반영됨</t>
         </is>
       </c>
-      <c r="E114" s="5"/>
-      <c r="F114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="4"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -2956,8 +3072,9 @@
           <t xml:space="preserve">워커가 죽어도 작업이 큐에 남고 재시작 시 이어짐</t>
         </is>
       </c>
-      <c r="E115" s="5"/>
-      <c r="F115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="4"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -2976,8 +3093,9 @@
         </is>
       </c>
       <c r="D116" s="4"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="E116" s="4"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1, 미구현</t>
         </is>
@@ -3004,8 +3122,9 @@
           <t xml:space="preserve">개발·배포 양쪽에서 같은 모델·차원으로 임베딩되고 모델 이름이 일치함</t>
         </is>
       </c>
-      <c r="E117" s="5"/>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="E117" s="4"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">두 경로(local-model·local-http)가 다른 이름을 남길 수 있음(관리/서빙경로_결정_SYS-002-4.md) — 경로가 섞이지 않았는지 특히 확인</t>
         </is>
@@ -3033,8 +3152,9 @@
 요청 단위 추적이 가능함</t>
         </is>
       </c>
-      <c r="E118" s="5"/>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="E118" s="4"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">워커에 request_id 미전달(재정님 담당, 미해결)로 3번 절차는 실패가 예상됨(2026-08-25 기준)</t>
         </is>
@@ -3057,8 +3177,9 @@
         </is>
       </c>
       <c r="D119" s="4"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="E119" s="4"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2, 미구현</t>
         </is>
@@ -3081,15 +3202,16 @@
         </is>
       </c>
       <c r="D120" s="4"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="E120" s="4"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3, 미구현</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F120"/>
+  <autoFilter ref="A4:G120"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/산출물/통합기능테스트명세서.xlsx
+++ b/산출물/통합기능테스트명세서.xlsx
@@ -93,15 +93,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="42" customWidth="1"/>
@@ -158,12 +158,12 @@
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-01</t>
+          <t xml:space="preserve">IT-AUTH-01</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인증부터 역할별 프로젝트 진입</t>
+          <t xml:space="preserve">회원가입·로그인·토큰 연동</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -173,17 +173,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회원가입 후 정상·오류 로그인을 수행한다.</t>
+          <t xml:space="preserve">가입부터 로그인·토큰 갱신·로그아웃까지 상태가 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 계정·중복 ID·틀린 비밀번호</t>
+          <t xml:space="preserve">신규 계정·정상 비밀번호</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 가입·로그인만 성공하고 오류 계약이 구분된다.</t>
+          <t xml:space="preserve">계정과 세션이 생성되고 로그아웃 후 토큰이 폐기된다.</t>
         </is>
       </c>
       <c r="H2" s="3"/>
@@ -200,17 +200,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">access 만료 후 refresh로 갱신하고 이전 refresh를 재사용한다.</t>
+          <t xml:space="preserve">중복 계정과 잘못된 인증정보를 거부하는지 확인한다.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효·사용 완료 refresh</t>
+          <t xml:space="preserve">중복 ID·이메일·틀린 비밀번호·누락/만료 토큰</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">토큰이 회전하며 이전 refresh는 401이다.</t>
+          <t xml:space="preserve">요청별 오류 코드로 차단되고 보호 API가 실행되지 않는다.</t>
         </is>
       </c>
       <c r="H3" s="3"/>
@@ -227,17 +227,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그아웃 뒤 같은 refresh로 다시 갱신한다.</t>
+          <t xml:space="preserve">refresh 토큰 회전과 저장 방식을 확인한다.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그아웃 세션</t>
+          <t xml:space="preserve">동일 사용자 refresh 2개·사용 완료 토큰</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재사용이 차단된다.</t>
+          <t xml:space="preserve">토큰은 매번 다르고 DB에는 해시만 저장되며 재사용은 차단된다.</t>
         </is>
       </c>
       <c r="H4" s="3"/>
@@ -245,26 +245,34 @@
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-PRJ-01</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 생성·역할·삭제 연동</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트를 생성하고 생성자 역할을 확인한다.</t>
+          <t xml:space="preserve">프로젝트 생성과 OWNER 등록이 함께 처리되는지 확인한다.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 프로젝트</t>
+          <t xml:space="preserve">신규 사용자·프로젝트명</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성자가 OWNER다.</t>
+          <t xml:space="preserve">프로젝트와 OWNER 멤버가 함께 생성되고 목록에 표시된다.</t>
         </is>
       </c>
       <c r="H5" s="3"/>
@@ -276,22 +284,22 @@
       <c r="C6" s="4"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">세 역할로 허용·금지 동작과 다른 프로젝트 직접 URL을 확인한다.</t>
+          <t xml:space="preserve">역할 변경이 프로젝트 권한에 즉시 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER·EDITOR·VIEWER·비멤버</t>
+          <t xml:space="preserve">OWNER·EDITOR·VIEWER</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">역할표와 일치하고 비멤버는 404다.</t>
+          <t xml:space="preserve">역할별 허용 동작만 실행되고 변경 직후 새 권한이 적용된다.</t>
         </is>
       </c>
       <c r="H6" s="3"/>
@@ -299,34 +307,26 @@
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-02</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 초대와 멤버 생명주기</t>
-        </is>
-      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER가 EDITOR 초대를 발송하고 중복 초대를 시도한다.</t>
+          <t xml:space="preserve">프로젝트 삭제 권한과 하위 데이터 정리를 확인한다.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 사용자 2회</t>
+          <t xml:space="preserve">문서·태스크가 있는 프로젝트</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">첫 초대만 생성되고 중복은 409다.</t>
+          <t xml:space="preserve">OWNER만 삭제할 수 있고 관련 데이터가 함께 정리된다.</t>
         </is>
       </c>
       <c r="H7" s="3"/>
@@ -334,16 +334,24 @@
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-PRJ-02</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초대·멤버 생명주기 연동</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">초대받은 사용자가 목록을 보고 수락한다.</t>
+          <t xml:space="preserve">초대 수락 시 프로젝트 멤버가 생성되는지 확인한다.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -353,7 +361,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멤버가 되고 프로젝트 목록에 나타난다.</t>
+          <t xml:space="preserve">초대가 ACCEPTED로 바뀌고 지정 역할의 멤버가 생성된다.</t>
         </is>
       </c>
       <c r="H8" s="3"/>
@@ -365,22 +373,22 @@
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 초대를 거절하고 OWNER가 보낸 초대를 취소한다.</t>
+          <t xml:space="preserve">중복 초대와 종료된 초대 재처리를 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 초대 2건</t>
+          <t xml:space="preserve">중복·거절·취소 초대</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REJECTED·CANCELLED가 보존되고 수락할 수 없다.</t>
+          <t xml:space="preserve">중복 생성과 거절·취소 후 수락이 차단된다.</t>
         </is>
       </c>
       <c r="H9" s="3"/>
@@ -388,26 +396,34 @@
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-DOC-01</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 업로드·텍스트 추출 연동</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER가 멤버 역할을 VIEWER로 바꾼다.</t>
+          <t xml:space="preserve">지원 파일 업로드부터 텍스트 추출 완료까지 연결되는지 확인한다.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDITOR 멤버</t>
+          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">즉시 편집 API가 403이다.</t>
+          <t xml:space="preserve">문서가 PENDING으로 저장된 뒤 EXTRACTED로 변경된다.</t>
         </is>
       </c>
       <c r="H10" s="3"/>
@@ -419,22 +435,22 @@
       <c r="C11" s="4"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멤버를 제외하고 기존 세션으로 재접근한다.</t>
+          <t xml:space="preserve">잘못된 업로드 입력을 저장 전에 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그인 유지 세션</t>
+          <t xml:space="preserve">20MB 초과·빈 파일·확장자 위장·경로 조작</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 프로젝트 경로가 404다.</t>
+          <t xml:space="preserve">입력별 오류 코드가 반환되고 파일과 문서 행이 남지 않는다.</t>
         </is>
       </c>
       <c r="H11" s="3"/>
@@ -442,34 +458,26 @@
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-03</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다중 업로드부터 21건 이상 목록</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지원 파일 5종을 다중 업로드한다.</t>
+          <t xml:space="preserve">추출 실패 상태와 재처리 흐름을 확인한다.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
+          <t xml:space="preserve">추출기 오류 문서</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 문서 ID가 즉시 반환되고 PENDING이다.</t>
+          <t xml:space="preserve">FAILED와 실패 사유가 저장되고 재시도 후 최종 상태로 변경된다.</t>
         </is>
       </c>
       <c r="H12" s="3"/>
@@ -481,22 +489,22 @@
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">형식·크기·빈 파일·중복·경로 조작 오류를 유도한다.</t>
+          <t xml:space="preserve">원문 제한과 문서 유형 정규화를 확인한다.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오류 파일 세트</t>
+          <t xml:space="preserve">제한 초과 DOCX·정상/미지원 유형</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 파일만 저장되고 원인별 오류다.</t>
+          <t xml:space="preserve">제한 초과는 차단되고 지원 유형만 표준값으로 저장된다.</t>
         </is>
       </c>
       <c r="H13" s="3"/>
@@ -504,26 +512,34 @@
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-OCR-01</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 전처리·구조화 연동</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker 처리 상태를 완료까지 조회한다.</t>
+          <t xml:space="preserve">문서 상태에 맞는 추출 전략을 선택하는지 확인한다.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트·스캔 문서</t>
+          <t xml:space="preserve">텍스트 PDF·희소 텍스트 스캔 PDF</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 방식과 EXTRACTED 상태가 기록된다.</t>
+          <t xml:space="preserve">native text 또는 전체 페이지 OCR 전략이 선택된다.</t>
         </is>
       </c>
       <c r="H14" s="3"/>
@@ -535,22 +551,22 @@
       <c r="C15" s="4"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 건을 실패시킨 뒤 재처리한다.</t>
+          <t xml:space="preserve">이미지 방향과 OCR 좌표를 같은 기준으로 저장하는지 확인한다.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출기 실패 문서</t>
+          <t xml:space="preserve">회전 EXIF 이미지·잘못된 좌표</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오류가 보이고 재처리 후 완료 또는 명시적 실패다.</t>
+          <t xml:space="preserve">정규화된 방향의 좌표만 저장되고 잘못된 좌표는 거부된다.</t>
         </is>
       </c>
       <c r="H15" s="3"/>
@@ -562,22 +578,22 @@
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서를 21건으로 만들고 2페이지로 이동한다.</t>
+          <t xml:space="preserve">단락·2단 문서·표의 읽기 구조가 유지되는지 확인한다.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21건·size 20</t>
+          <t xml:space="preserve">새 박스·2단 페이지·표 OCR</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1페이지 20건, 2페이지 1건이며 URL page가 유지된다.</t>
+          <t xml:space="preserve">본문 순서와 행·열 구조가 청킹까지 유지된다.</t>
         </is>
       </c>
       <c r="H16" s="3"/>
@@ -585,26 +601,34 @@
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-OCR-02</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 검수·재인덱싱 연동</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필터를 변경하고 새로고침한다.</t>
+          <t xml:space="preserve">박스 편집과 재OCR 결과가 확정 본문에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2페이지에서 유형 필터</t>
+          <t xml:space="preserve">박스 생성·제외·복원·재OCR</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">page가 초기화되고 필터 상태가 일관된다.</t>
+          <t xml:space="preserve">사용자가 확정한 요소만 읽기 순서대로 본문에 반영된다.</t>
         </is>
       </c>
       <c r="H17" s="3"/>
@@ -612,34 +636,26 @@
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="3"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-04</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 수정부터 최신 검색 반영</t>
-        </is>
-      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 화면에서 이미지·박스·신뢰도를 확인하고 확대한다.</t>
+          <t xml:space="preserve">동시 수정과 일괄 수정 실패의 원자성을 확인한다.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스캔 문서</t>
+          <t xml:space="preserve">같은 version 요청·정상 1건과 stale 1건</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 배율에서 박스와 문자가 일치한다.</t>
+          <t xml:space="preserve">오래된 요청은 거부되고 일괄 수정은 전체 롤백된다.</t>
         </is>
       </c>
       <c r="H18" s="3"/>
@@ -651,22 +667,22 @@
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트·좌표·단락·읽기 순서를 수정한다.</t>
+          <t xml:space="preserve">검수 완료가 버전 변경과 재청킹 작업으로 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오탈자·2단·표 문서</t>
+          <t xml:space="preserve">수정 완료 문서</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 보존, version 증가, 본문 순서가 정확하다.</t>
+          <t xml:space="preserve">text_version이 증가하고 기존 청크가 stale 처리된 뒤 재청킹된다.</t>
         </is>
       </c>
       <c r="H19" s="3"/>
@@ -678,22 +694,22 @@
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스를 생성·제외·복원하고 병합·분리한다.</t>
+          <t xml:space="preserve">재인덱싱 전후 검색 결과가 섞이지 않는지 확인한다.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 요소 다건</t>
+          <t xml:space="preserve">수정 전 문구·수정 후 문구</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 포함 요소만 확정 본문에 반영된다.</t>
+          <t xml:space="preserve">낡은 근거는 최신으로 표시되지 않고 새 청크만 검색된다.</t>
         </is>
       </c>
       <c r="H20" s="3"/>
@@ -701,26 +717,34 @@
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-ANL-01</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 요약·분류·분석 상태 연동</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 세션에서 같은 요소를 수정한다.</t>
+          <t xml:space="preserve">요약·분류·일정 분석 결과가 저장되는지 확인한다.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 version 동시 요청</t>
+          <t xml:space="preserve">요약·유형·날짜가 있는 문서</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나중 요청은 409이며 부분 변경이 없다.</t>
+          <t xml:space="preserve">분석별 구조화 결과와 근거가 저장된다.</t>
         </is>
       </c>
       <c r="H21" s="3"/>
@@ -732,22 +756,22 @@
       <c r="C22" s="4"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수를 완료하고 재청킹 상태를 확인한다.</t>
+          <t xml:space="preserve">근거·schema·날짜 후보가 잘못된 응답을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 완료 문서</t>
+          <t xml:space="preserve">무근거 인용·깨진 JSON·없는 날짜 ID</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 리비전과 재인덱싱 작업이 연결된다.</t>
+          <t xml:space="preserve">AI_INVALID_RESPONSE로 처리되고 잘못된 결과는 저장되지 않는다.</t>
         </is>
       </c>
       <c r="H22" s="3"/>
@@ -759,22 +783,22 @@
       <c r="C23" s="4"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색에서 수정 전·후 문구를 조회한다.</t>
+          <t xml:space="preserve">원문 변경과 일부 분석 실패 상태를 구분하는지 확인한다.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이전 문구·새 문구</t>
+          <t xml:space="preserve">분석 중 원문 변경·분석기 1개 실패</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 근거만 최신 결과로 표시된다.</t>
+          <t xml:space="preserve">원문 변경은 중단되고 일부 실패는 PARTIAL로 기록된다.</t>
         </is>
       </c>
       <c r="H23" s="3"/>
@@ -784,12 +808,12 @@
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-05</t>
+          <t xml:space="preserve">IT-ANL-02</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항·일정 분석과 검토</t>
+          <t xml:space="preserve">결정사항·일정 검토 연동</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -799,17 +823,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회의록 분석을 실행하고 job 상태를 조회한다.</t>
+          <t xml:space="preserve">결정 후보의 검토 상태 전이를 확인한다.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정·일정 포함 회의록</t>
+          <t xml:space="preserve">PENDING 결정 4건</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 분석기가 완료되고 PENDING 후보가 생긴다.</t>
+          <t xml:space="preserve">승인·수정 승인·거절·취소와 결정자·시각이 저장된다.</t>
         </is>
       </c>
       <c r="H24" s="3"/>
@@ -826,17 +850,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 후보를 승인·수정 승인·거절·취소한다.</t>
+          <t xml:space="preserve">일정 후보의 검토 상태 전이를 확인한다.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 후보 4건</t>
+          <t xml:space="preserve">PENDING 일정 4건</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태·결정자·시각이 기록된다.</t>
+          <t xml:space="preserve">각 검토 상태와 수정값이 저장된다.</t>
         </is>
       </c>
       <c r="H25" s="3"/>
@@ -853,17 +877,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일정 후보도 같은 네 상태로 처리한다.</t>
+          <t xml:space="preserve">검토 완료 상태만 하류 기능에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일정 후보 4건</t>
+          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 항목만 하류 데이터가 된다.</t>
+          <t xml:space="preserve">승인·수정 승인 항목만 대장과 산출물에 포함된다.</t>
         </is>
       </c>
       <c r="H26" s="3"/>
@@ -871,26 +895,34 @@
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-TSK-01</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액션 아이템·태스크 연동</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 대장과 다음 회의 안건을 미리 본다.</t>
+          <t xml:space="preserve">대상 문서에서 원문 근거가 있는 액션 후보만 생성하는지 확인한다.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 결정·PENDING 도메인 결정</t>
+          <t xml:space="preserve">계약서·회의록·후보 없는 문서</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대장은 승인 결정 전체, 안건은 PENDING 결정만 포함한다.</t>
+          <t xml:space="preserve">대상 계약의 근거 후보만 생성되고 후보가 없으면 모델을 호출하지 않는다.</t>
         </is>
       </c>
       <c r="H27" s="3"/>
@@ -902,22 +934,22 @@
       <c r="C28" s="4"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 완료 뒤 대시보드·산출물 화면을 다시 연다.</t>
+          <t xml:space="preserve">재분석 시 미검토 후보만 교체하는지 확인한다.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLETED job</t>
+          <t xml:space="preserve">PENDING·APPROVED 후보</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 승인 대기·산출물 재료가 새로고침된다.</t>
+          <t xml:space="preserve">PENDING만 교체되고 검토 완료 이력은 유지된다.</t>
         </is>
       </c>
       <c r="H28" s="3"/>
@@ -925,34 +957,26 @@
     </row>
     <row r="29" ht="38" customHeight="1">
       <c r="A29" s="3"/>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-06</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">액션 아이템 제안에서 태스크 완료까지</t>
-        </is>
-      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 문서를 분석해 PENDING 액션 제안을 만든다.</t>
+          <t xml:space="preserve">후보 승인·거절이 태스크 보드에 맞게 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명시적 수행 의무가 있는 계약서</t>
+          <t xml:space="preserve">PENDING 제안 2건</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 근거가 있는 후보만 생성된다.</t>
+          <t xml:space="preserve">승인 항목은 태스크 1건이 되고 거절 항목은 보드에 나타나지 않는다.</t>
         </is>
       </c>
       <c r="H29" s="3"/>
@@ -960,26 +984,34 @@
     </row>
     <row r="30" ht="38" customHeight="1">
       <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-AMT-01</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 추출·검증·재분석 연동</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제안 하나를 승인한다.</t>
+          <t xml:space="preserve">정상 금액 응답을 PENDING 항목으로 저장하는지 확인한다.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안</t>
+          <t xml:space="preserve">문자열 숫자가 포함된 정상 JSON</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_APPROVED 태스크 한 건이 생긴다.</t>
+          <t xml:space="preserve">숫자가 정규화되고 source revision과 함께 저장된다.</t>
         </is>
       </c>
       <c r="H30" s="3"/>
@@ -991,22 +1023,22 @@
       <c r="C31" s="4"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 제안을 거절한다.</t>
+          <t xml:space="preserve">비표준·미지원 금액 응답을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안</t>
+          <t xml:space="preserve">코드펜스·잘못된 root·NaN·unknown·음수</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보드에는 안 보이고 거절 이력에 남는다.</t>
+          <t xml:space="preserve">AI_INVALID_RESPONSE이며 금액 항목이 저장되지 않는다.</t>
         </is>
       </c>
       <c r="H31" s="3"/>
@@ -1018,22 +1050,22 @@
       <c r="C32" s="4"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">태스크를 수정하고 칸반에서 DONE으로 옮긴다.</t>
+          <t xml:space="preserve">재분석 시 미검토 금액만 교체하는지 확인한다.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인된 태스크</t>
+          <t xml:space="preserve">PENDING·APPROVED 혼합</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태와 completed_at이 기록된다.</t>
+          <t xml:space="preserve">PENDING만 교체되고 검토 이력은 보존된다.</t>
         </is>
       </c>
       <c r="H32" s="3"/>
@@ -1041,26 +1073,34 @@
     </row>
     <row r="33" ht="38" customHeight="1">
       <c r="A33" s="3"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-AMT-02</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 계산·검토·집계 연동</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 문서를 재분석한다.</t>
+          <t xml:space="preserve">수량·단가·VAT와 기재 금액을 검산하는지 확인한다.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 근거</t>
+          <t xml:space="preserve">공급가액·VAT·불일치 금액</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 완료 후보·태스크는 중복 생성되지 않는다.</t>
+          <t xml:space="preserve">VAT 제외 합계와 불일치가 표시되고 원값은 유지된다.</t>
         </is>
       </c>
       <c r="H33" s="3"/>
@@ -1068,34 +1108,26 @@
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="A34" s="3"/>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-07</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 추출·검토·권한·화면 갱신</t>
-        </is>
-      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 분석을 실행하고 PENDING 결과를 확인한다.</t>
+          <t xml:space="preserve">혼합 통화와 계산 경계를 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량·단가·총액·부가세 문서</t>
+          <t xml:space="preserve">KRW·USD 혼합 문서</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 근거와 revision을 가진 PENDING 항목이 생긴다.</t>
+          <t xml:space="preserve">통화가 섞인 집계는 오류로 처리된다.</t>
         </is>
       </c>
       <c r="H34" s="3"/>
@@ -1107,22 +1139,22 @@
       <c r="C35" s="4"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인·거절·취소를 각각 수행한다.</t>
+          <t xml:space="preserve">금액 검토 상태와 권한이 집계에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">후보 4건</t>
+          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED·VIEWER</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 상태와 수정 가능 필드 계약이 지켜진다.</t>
+          <t xml:space="preserve">승인·수정 승인만 집계되고 VIEWER의 제한 경로는 차단된다.</t>
         </is>
       </c>
       <c r="H35" s="3"/>
@@ -1134,22 +1166,22 @@
       <c r="C36" s="4"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 현황에서 합계·부가세·원가구분·불일치를 확인한다.</t>
+          <t xml:space="preserve">재분석 유효 snapshot을 원자적으로 전환하는지 확인한다.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 완료 항목</t>
+          <t xml:space="preserve">이전 완료 분석·신규 일부/전체 검토</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인만 정확히 집계된다.</t>
+          <t xml:space="preserve">부분 검토 중 기존 합계를 유지하고 완료 후 새 snapshot으로 전환된다.</t>
         </is>
       </c>
       <c r="H36" s="3"/>
@@ -1157,26 +1189,34 @@
     </row>
     <row r="37" ht="38" customHeight="1">
       <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-SRH-01</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 조회·하이브리드 검색 연동</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출처 파일·원문 인용·계산식을 확인한다.</t>
+          <t xml:space="preserve">문서 목록 페이징과 필터 상태가 일치하는지 확인한다.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량×단가 항목</t>
+          <t xml:space="preserve">문서 21건·size 20·유형 필터</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 금액의 근거가 함께 표시된다.</t>
+          <t xml:space="preserve">페이지 건수와 URL 상태가 맞고 필터 변경 시 첫 페이지로 이동한다.</t>
         </is>
       </c>
       <c r="H37" s="3"/>
@@ -1188,22 +1228,22 @@
       <c r="C38" s="4"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER로 탭·직접 URL·API에 접근한다.</t>
+          <t xml:space="preserve">문단과 표 구조를 유지해 검색 청크를 만드는지 확인한다.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER 계정</t>
+          <t xml:space="preserve">문단·표 구조 요소</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 현황은 차단되고 정책 예외인 선례 조회만 허용된다.</t>
+          <t xml:space="preserve">표 행이 깨지지 않고 구조 경계가 유지된다.</t>
         </is>
       </c>
       <c r="H38" s="3"/>
@@ -1215,22 +1255,22 @@
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 완료 후 페이지 이동 없이 현황을 확인한다.</t>
+          <t xml:space="preserve">벡터·키워드 검색과 재순위가 연결되는지 확인한다.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLETED job</t>
+          <t xml:space="preserve">키워드·의미 혼합 질의</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액·대시보드·산출물 cache가 새 값으로 갱신된다.</t>
+          <t xml:space="preserve">두 결과가 융합되고 reranker 순서로 반환된다.</t>
         </is>
       </c>
       <c r="H39" s="3"/>
@@ -1238,34 +1278,26 @@
     </row>
     <row r="40" ht="38" customHeight="1">
       <c r="A40" s="3"/>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-08</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 재분석 유효 스냅샷 전환</t>
-        </is>
-      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">완료된 기존 금액 snapshot의 합계를 기록한다.</t>
+          <t xml:space="preserve">검색 경계와 장애 fallback을 확인한다.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 A 전체 검토 완료</t>
+          <t xml:space="preserve">%·_ 검색어·reranker 오류·평가 질의</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기준 합계가 표시된다.</t>
+          <t xml:space="preserve">와일드카드는 escape되고 장애 시 융합 순서로 결과를 반환한다.</t>
         </is>
       </c>
       <c r="H40" s="3"/>
@@ -1273,26 +1305,34 @@
     </row>
     <row r="41" ht="38" customHeight="1">
       <c r="A41" s="3"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-CHAT-01</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 제한 질의응답 연동</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 문서를 재분석하고 신규 항목 한 건만 승인한다.</t>
+          <t xml:space="preserve">예산 안에서 조립한 근거만 답변에 사용하는지 확인한다.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 B 일부 검토</t>
+          <t xml:space="preserve">긴 청크 다건·budget 4000</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존 완료 합계를 유지한다.</t>
+          <t xml:space="preserve">예산을 넘지 않고 조립된 evidence만 인용한다.</t>
         </is>
       </c>
       <c r="H41" s="3"/>
@@ -1304,22 +1344,22 @@
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나머지 신규 항목을 승인·거절해 검토를 끝낸다.</t>
+          <t xml:space="preserve">검색 결과가 없을 때 모델 호출을 생략하는지 확인한다.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 B 전체 검토</t>
+          <t xml:space="preserve">검색 결과 0건</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 B snapshot으로 한 번에 전환된다.</t>
+          <t xml:space="preserve">근거 없음으로 응답하고 모델을 호출하지 않는다.</t>
         </is>
       </c>
       <c r="H42" s="3"/>
@@ -1331,22 +1371,22 @@
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 snapshot을 전부 거절한다.</t>
+          <t xml:space="preserve">허용 범위 밖 근거를 가진 답변을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 C 전체 거절</t>
+          <t xml:space="preserve">조립하지 않은 evidence ID</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 금액 0건으로 전환된다.</t>
+          <t xml:space="preserve">잘못된 답변은 저장·표시되지 않고 보류 응답을 반환한다.</t>
         </is>
       </c>
       <c r="H43" s="3"/>
@@ -1354,26 +1394,34 @@
     </row>
     <row r="44" ht="38" customHeight="1">
       <c r="A44" s="3"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-LAB-01</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인원·기간·투입률 인건비 계산 연동</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 프로젝트에도 같은 문서명·금액을 둔다.</t>
+          <t xml:space="preserve">명시 인월과 기술자별 인월을 계산하는지 확인한다.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 2개</t>
+          <t xml:space="preserve">9,500,000원×6인월·기술자 2명</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서로의 집계가 섞이지 않는다.</t>
+          <t xml:space="preserve">각 단가와 인월에 맞는 금액과 근거가 반환된다.</t>
         </is>
       </c>
       <c r="H44" s="3"/>
@@ -1381,34 +1429,26 @@
     </row>
     <row r="45" ht="38" customHeight="1">
       <c r="A45" s="3"/>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-09</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하이브리드 검색과 원문 이동</t>
-        </is>
-      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유 문서번호로 키워드 검색한다.</t>
+          <t xml:space="preserve">인원·개월·투입률을 유효 인월로 계산하는지 확인한다.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유번호</t>
+          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확 문자열 결과와 match 위치가 표시된다.</t>
+          <t xml:space="preserve">유효 3인월과 28,500,000원이 반환된다.</t>
         </is>
       </c>
       <c r="H45" s="3"/>
@@ -1420,22 +1460,22 @@
       <c r="C46" s="4"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의미 질의로 검색한다.</t>
+          <t xml:space="preserve">모호한 매핑과 투입률 경계를 임의 계산하지 않는지 확인한다.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 해지 조건</t>
+          <t xml:space="preserve">이름 매핑 없음·0%·100%·120%·1.5인월</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">관련 의미 청크가 상위에 나온다.</t>
+          <t xml:space="preserve">유효 범위만 계산하고 모호한 경우 명확화를 요청한다.</t>
         </is>
       </c>
       <c r="H46" s="3"/>
@@ -1443,26 +1483,34 @@
     </row>
     <row r="47" ht="38" customHeight="1">
       <c r="A47" s="3"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-DLV-01</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드 연동</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하이브리드 검색과 reranker 순서를 확인한다.</t>
+          <t xml:space="preserve">현재 DB 자료로 프로젝트 현황 미리보기를 만드는지 확인한다.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">키워드·의미 혼합 질의</t>
+          <t xml:space="preserve">PROJECT_STATUS·프로젝트·태스크·일정</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">양쪽 결과가 융합·재순위된다.</t>
+          <t xml:space="preserve">기간 없이 다섯 절과 현재 자료 표가 생성된다.</t>
         </is>
       </c>
       <c r="H47" s="3"/>
@@ -1474,22 +1522,22 @@
       <c r="C48" s="4"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거를 눌러 원문으로 이동한다.</t>
+          <t xml:space="preserve">출력 형식별 내용과 데이터형이 일치하는지 확인한다.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과 1건</t>
+          <t xml:space="preserve">MD·HTML·XLSX·PDF</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">해당 문서·인용 위치가 확인된다.</t>
+          <t xml:space="preserve">절과 자료가 같고 XLSX 금액은 숫자 셀로 생성된다.</t>
         </is>
       </c>
       <c r="H48" s="3"/>
@@ -1501,22 +1549,22 @@
       <c r="C49" s="4"/>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비멤버 프로젝트 ID로 같은 검색을 호출한다.</t>
+          <t xml:space="preserve">원천 자료 변경과 미리보기 건수 규칙을 확인한다.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타 프로젝트 ID</t>
+          <t xml:space="preserve">생성 후 자료 추가·재분석 금액</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404이며 결과가 노출되지 않는다.</t>
+          <t xml:space="preserve">stale가 표시되고 count와 본문이 같은 유효 snapshot을 사용한다.</t>
         </is>
       </c>
       <c r="H49" s="3"/>
@@ -1524,34 +1572,26 @@
     </row>
     <row r="50" ht="38" customHeight="1">
       <c r="A50" s="3"/>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-10</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">근거 제한 질의응답</t>
-        </is>
-      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거가 있는 질문을 하고 evidence를 연다.</t>
+          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드를 확인한다.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">본문에 답이 있는 질문</t>
+          <t xml:space="preserve">네 출력 형식·생성된 산출물 ID</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">답변 인용이 실제 청크와 일치한다.</t>
+          <t xml:space="preserve">네 파일이 이력에 남고 제목 기반 파일명으로 다시 다운로드된다.</t>
         </is>
       </c>
       <c r="H50" s="3"/>
@@ -1559,26 +1599,34 @@
     </row>
     <row r="51" ht="38" customHeight="1">
       <c r="A51" s="3"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-SYS-01</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오류 응답·request_id·worker 복구 연동</t>
+        </is>
+      </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과가 없는 질문을 한다.</t>
+          <t xml:space="preserve">API 오류 응답 형식과 request_id를 확인한다.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 밖 질문</t>
+          <t xml:space="preserve">404·405·409·422·middleware 없는 요청</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LLM 호출 없이 근거 없음으로 답한다.</t>
+          <t xml:space="preserve">code·message·request_id가 같은 구조로 반환된다.</t>
         </is>
       </c>
       <c r="H51" s="3"/>
@@ -1590,22 +1638,22 @@
       <c r="C52" s="4"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용 evidence 밖 ID를 반환하도록 오류 응답을 주입한다.</t>
+          <t xml:space="preserve">request_id가 API에서 worker 로그까지 전달되는지 확인한다.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">조작된 모델 응답</t>
+          <t xml:space="preserve">고정 X-Request-ID 재처리 요청</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잘못된 근거 답변이 사용자에게 전달되지 않는다.</t>
+          <t xml:space="preserve">API·queue·worker 로그에 같은 ID가 기록된다.</t>
         </is>
       </c>
       <c r="H52" s="3"/>
@@ -1617,22 +1665,22 @@
       <c r="C53" s="4"/>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">answerable=false 응답의 문구를 확인한다.</t>
+          <t xml:space="preserve">worker와 AI 공급자 장애를 구분해 복구하는지 확인한다.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 없는 응답</t>
+          <t xml:space="preserve">worker 중단·Ollama 연결 실패·schema 오류</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">단정적 숫자·사실을 말하지 않는다.</t>
+          <t xml:space="preserve">작업은 유실되지 않고 provider와 응답 형식 오류가 구분된다.</t>
         </is>
       </c>
       <c r="H53" s="3"/>
@@ -1640,26 +1688,34 @@
     </row>
     <row r="54" ht="38" customHeight="1">
       <c r="A54" s="3"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-ISO-01</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 데이터 격리 연동</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업일지의 755 질문을 같은 문서로 재현한다.</t>
+          <t xml:space="preserve">다른 프로젝트 리소스에 접근할 수 없는지 확인한다.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 질문·동일 원문</t>
+          <t xml:space="preserve">타 프로젝트 문서·OCR·분석·금액·검색·산출물 ID</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755를 근거 없이 답하지 않으며 근거 ID를 요구한다.</t>
+          <t xml:space="preserve">모든 경로가 404이며 데이터가 노출되지 않는다.</t>
         </is>
       </c>
       <c r="H54" s="3"/>
@@ -1667,34 +1723,26 @@
     </row>
     <row r="55" ht="38" customHeight="1">
       <c r="A55" s="3"/>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-11</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인원×기간×투입률 인건비 계산</t>
-        </is>
-      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명시 인월 질문을 한다.</t>
+          <t xml:space="preserve">중복 파일 검사가 프로젝트 안에서만 적용되는지 확인한다.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9,500,000원×6인월</t>
+          <t xml:space="preserve">같은 hash·프로젝트 2개</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57,000,000원과 근거가 표시된다.</t>
+          <t xml:space="preserve">각 프로젝트에는 한 번씩 업로드할 수 있다.</t>
         </is>
       </c>
       <c r="H55" s="3"/>
@@ -1706,449 +1754,63 @@
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인원·개월·투입률 질문을 한다.</t>
+          <t xml:space="preserve">멤버 제외 직후 기존 세션 접근을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
+          <t xml:space="preserve">제외 전 로그인 세션·열린 화면</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28,500,000원과 유효 3인월이 표시된다.</t>
+          <t xml:space="preserve">기존 토큰과 화면에서도 프로젝트 접근이 즉시 차단된다.</t>
         </is>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="A57" s="3"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">복수 기술자에 서로 다른 인월을 질문한다.</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기술자 2명·인월 2개</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이름별 올바른 단가와 수량을 매핑한다.</t>
-        </is>
-      </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" ht="38" customHeight="1">
-      <c r="A58" s="3"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모호·범위 밖 투입률을 질문한다.</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">복수 50/70%, 120%</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임의 계산하지 않고 명확화를 요청한다.</t>
-        </is>
-      </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" ht="38" customHeight="1">
-      <c r="A59" s="3"/>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-12</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물 화면에서 프로젝트 현황을 선택하고 기간 없이 건수·본문을 미리 본다.</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PROJECT_STATUS</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기간을 요구하지 않고 현재 자료를 보여준다.</t>
-        </is>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" ht="38" customHeight="1">
-      <c r="A60" s="3"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">본문 상단 다섯 절을 확인한다.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트·태스크·일정 자료</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 기본 정보·진행 상태 요약·주요 성과·일정 이슈·향후 계획이 DB 값으로 생성된다.</t>
-        </is>
-      </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" ht="38" customHeight="1">
-      <c r="A61" s="3"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상세 표의 문서·태스크·결정·일정·금액을 확인한다.</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">승인·대기·거절 자료 혼합</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">승인 계약과 유효 snapshot에 맞는 현재 자료만 포함된다.</t>
-        </is>
-      </c>
-      <c r="H61" s="3"/>
-      <c r="I61" s="2"/>
-    </row>
-    <row r="62" ht="38" customHeight="1">
-      <c r="A62" s="3"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MD·HTML·XLSX·PDF로 프로젝트 현황을 생성한다.</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네 출력 형식</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네 형식 모두 같은 절과 자료를 가진 파일이 생성된다.</t>
-        </is>
-      </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="63" ht="38" customHeight="1">
-      <c r="A63" s="3"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이력에서 파일을 다시 내려받고 VIEWER로도 다운로드한다.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생성된 산출물 ID</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제목 기반 파일명으로 다운로드되며 VIEWER 조회는 허용된다.</t>
-        </is>
-      </c>
-      <c r="H63" s="3"/>
-      <c r="I63" s="2"/>
-    </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">원천 자료 추가와 201건 이상 절을 확인한다.</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생성 후 문서 추가·항목 201건</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stale가 표시되고 200건 상한이면 생략 건수가 사용자에게 안내된다.</t>
-        </is>
-      </c>
-      <c r="H64" s="3"/>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" ht="38" customHeight="1">
-      <c r="A65" s="3"/>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-13</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">worker 재시작·request_id·AI 오류 구분</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고정 X-Request-ID로 문서 업로드를 시작한다.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">request_id=tasqra-e2e-001</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 응답·extract·chunk worker 로그가 같은 ID다.</t>
-        </is>
-      </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="2"/>
-    </row>
-    <row r="66" ht="38" customHeight="1">
-      <c r="A66" s="3"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실패 문서를 같은 ID로 재처리한다.</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">retry API</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재처리 worker에도 같은 ID가 전달된다.</t>
-        </is>
-      </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="2"/>
-    </row>
-    <row r="67" ht="38" customHeight="1">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">처리 중 worker를 종료하고 다시 시작한다.</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">queued/running job</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작업이 유실되지 않고 완료 또는 명시적 실패로 수렴한다.</t>
-        </is>
-      </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="2"/>
-    </row>
-    <row r="68" ht="38" customHeight="1">
-      <c r="A68" s="3"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Docker worker에서 Ollama 정상 구조화 응답을 받는다.</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정상 json_schema 응답</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">분석 결과가 저장된다.</t>
-        </is>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="2"/>
-    </row>
-    <row r="69" ht="38" customHeight="1">
-      <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ollama 연결 주소를 실패시키고 호출한다.</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">연결 거부</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI_PROVIDER_ERROR로 구분된다.</t>
-        </is>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="2"/>
-    </row>
-    <row r="70" ht="38" customHeight="1">
-      <c r="A70" s="3"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">연결은 되지만 malformed JSON을 반환한다.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schema 위반 응답</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE이며 원문·응답 전문은 로그에 노출되지 않는다.</t>
-        </is>
-      </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="C18:C23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B45:B49"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="C59:C64"/>
-    <mergeCell ref="B65:B70"/>
-    <mergeCell ref="C65:C70"/>
+  <mergeCells count="34">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="C54:C56"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>

--- a/산출물/통합기능테스트명세서.xlsx
+++ b/산출물/통합기능테스트명세서.xlsx
@@ -93,7 +93,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -398,12 +398,12 @@
       <c r="A10" s="3"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-DOC-01</t>
+          <t xml:space="preserve">IT-DSH-01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 업로드·텍스트 추출 연동</t>
+          <t xml:space="preserve">월간 캘린더 조회 연동</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -413,17 +413,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지원 파일 업로드부터 텍스트 추출 완료까지 연결되는지 확인한다.</t>
+          <t xml:space="preserve">월 이동 범위에 맞는 태스크와 승인 일정을 조회하는지 확인한다.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
+          <t xml:space="preserve">42일 범위·TASK_DUE·APPROVED/EDITED 일정</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서가 PENDING으로 저장된 뒤 EXTRACTED로 변경된다.</t>
+          <t xml:space="preserve">조회 범위의 태스크와 승인 일정만 공통 캘린더 응답으로 반환된다.</t>
         </is>
       </c>
       <c r="H10" s="3"/>
@@ -440,17 +440,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잘못된 업로드 입력을 저장 전에 차단하는지 확인한다.</t>
+          <t xml:space="preserve">기간 일정과 기한 일정의 날짜 배치를 확인한다.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20MB 초과·빈 파일·확장자 위장·경로 조작</t>
+          <t xml:space="preserve">월 경계를 걸친 PERIOD·DEADLINE·날짜 없는 일정</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">입력별 오류 코드가 반환되고 파일과 문서 행이 남지 않는다.</t>
+          <t xml:space="preserve">기간은 겹치는 모든 날짜에, 기한은 종료일에 표시되고 날짜 없는 일정은 제외된다.</t>
         </is>
       </c>
       <c r="H11" s="3"/>
@@ -467,17 +467,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 실패 상태와 재처리 흐름을 확인한다.</t>
+          <t xml:space="preserve">캘린더 권한·기간 오류와 태스크 보드 이동을 확인한다.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출기 오류 문서</t>
+          <t xml:space="preserve">from&gt;to·비멤버·태스크 ID</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED와 실패 사유가 저장되고 재시도 후 최종 상태로 변경된다.</t>
+          <t xml:space="preserve">잘못된 기간은 422, 비멤버는 차단되고 태스크 선택 시 보드의 해당 카드로 이동한다.</t>
         </is>
       </c>
       <c r="H12" s="3"/>
@@ -485,26 +485,34 @@
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="3"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-DOC-01</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 업로드·텍스트 추출 연동</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 제한과 문서 유형 정규화를 확인한다.</t>
+          <t xml:space="preserve">지원 파일 업로드부터 텍스트 추출 완료까지 연결되는지 확인한다.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제한 초과 DOCX·정상/미지원 유형</t>
+          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제한 초과는 차단되고 지원 유형만 표준값으로 저장된다.</t>
+          <t xml:space="preserve">문서가 PENDING으로 저장된 뒤 EXTRACTED로 변경된다.</t>
         </is>
       </c>
       <c r="H13" s="3"/>
@@ -512,34 +520,26 @@
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="3"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-OCR-01</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 전처리·구조화 연동</t>
-        </is>
-      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 상태에 맞는 추출 전략을 선택하는지 확인한다.</t>
+          <t xml:space="preserve">잘못된 업로드 입력을 저장 전에 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트 PDF·희소 텍스트 스캔 PDF</t>
+          <t xml:space="preserve">20MB 초과·빈 파일·확장자 위장·경로 조작</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native text 또는 전체 페이지 OCR 전략이 선택된다.</t>
+          <t xml:space="preserve">입력별 오류 코드가 반환되고 파일과 문서 행이 남지 않는다.</t>
         </is>
       </c>
       <c r="H14" s="3"/>
@@ -551,22 +551,22 @@
       <c r="C15" s="4"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지 방향과 OCR 좌표를 같은 기준으로 저장하는지 확인한다.</t>
+          <t xml:space="preserve">추출 실패 상태와 재처리 흐름을 확인한다.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회전 EXIF 이미지·잘못된 좌표</t>
+          <t xml:space="preserve">추출기 오류 문서</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정규화된 방향의 좌표만 저장되고 잘못된 좌표는 거부된다.</t>
+          <t xml:space="preserve">FAILED와 실패 사유가 저장되고 재시도 후 최종 상태로 변경된다.</t>
         </is>
       </c>
       <c r="H15" s="3"/>
@@ -578,22 +578,22 @@
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">단락·2단 문서·표의 읽기 구조가 유지되는지 확인한다.</t>
+          <t xml:space="preserve">원문 제한과 문서 유형 정규화를 확인한다.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 박스·2단 페이지·표 OCR</t>
+          <t xml:space="preserve">제한 초과 DOCX·정상/미지원 유형</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">본문 순서와 행·열 구조가 청킹까지 유지된다.</t>
+          <t xml:space="preserve">제한 초과는 차단되고 지원 유형만 표준값으로 저장된다.</t>
         </is>
       </c>
       <c r="H16" s="3"/>
@@ -601,34 +601,26 @@
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="3"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-OCR-02</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 검수·재인덱싱 연동</t>
-        </is>
-      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 편집과 재OCR 결과가 확정 본문에 반영되는지 확인한다.</t>
+          <t xml:space="preserve">문서 목록과 OCR 검수 조회의 쿼리 수가 데이터 건수에 비례해 늘지 않는지 확인한다.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 생성·제외·복원·재OCR</t>
+          <t xml:space="preserve">문서 1·20·100건·OCR 요소 다건</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자가 확정한 요소만 읽기 순서대로 본문에 반영된다.</t>
+          <t xml:space="preserve">목록은 일괄 조회하고 검수 데이터는 미리 불러와 쿼리 수가 일정한 범위에 머문다.</t>
         </is>
       </c>
       <c r="H17" s="3"/>
@@ -636,26 +628,34 @@
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-OCR-01</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 전처리·구조화 연동</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동시 수정과 일괄 수정 실패의 원자성을 확인한다.</t>
+          <t xml:space="preserve">문서 상태에 맞는 추출 전략을 선택하는지 확인한다.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 version 요청·정상 1건과 stale 1건</t>
+          <t xml:space="preserve">텍스트 PDF·희소 텍스트 스캔 PDF</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오래된 요청은 거부되고 일괄 수정은 전체 롤백된다.</t>
+          <t xml:space="preserve">native text 또는 전체 페이지 OCR 전략이 선택된다.</t>
         </is>
       </c>
       <c r="H18" s="3"/>
@@ -667,22 +667,22 @@
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 완료가 버전 변경과 재청킹 작업으로 이어지는지 확인한다.</t>
+          <t xml:space="preserve">이미지 방향과 OCR 좌표를 같은 기준으로 저장하는지 확인한다.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 완료 문서</t>
+          <t xml:space="preserve">회전 EXIF 이미지·잘못된 좌표</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text_version이 증가하고 기존 청크가 stale 처리된 뒤 재청킹된다.</t>
+          <t xml:space="preserve">정규화된 방향의 좌표만 저장되고 잘못된 좌표는 거부된다.</t>
         </is>
       </c>
       <c r="H19" s="3"/>
@@ -694,22 +694,22 @@
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재인덱싱 전후 검색 결과가 섞이지 않는지 확인한다.</t>
+          <t xml:space="preserve">단락·2단 문서·표의 읽기 구조가 유지되는지 확인한다.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 전 문구·수정 후 문구</t>
+          <t xml:space="preserve">새 박스·2단 페이지·표 OCR</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">낡은 근거는 최신으로 표시되지 않고 새 청크만 검색된다.</t>
+          <t xml:space="preserve">본문 순서와 행·열 구조가 청킹까지 유지된다.</t>
         </is>
       </c>
       <c r="H20" s="3"/>
@@ -719,12 +719,12 @@
       <c r="A21" s="3"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-ANL-01</t>
+          <t xml:space="preserve">IT-OCR-02</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 요약·분류·분석 상태 연동</t>
+          <t xml:space="preserve">OCR 검수·재인덱싱 연동</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -734,17 +734,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">요약·분류·일정 분석 결과가 저장되는지 확인한다.</t>
+          <t xml:space="preserve">박스 편집과 재OCR 결과가 확정 본문에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">요약·유형·날짜가 있는 문서</t>
+          <t xml:space="preserve">박스 생성·제외·복원·재OCR</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석별 구조화 결과와 근거가 저장된다.</t>
+          <t xml:space="preserve">사용자가 확정한 요소만 읽기 순서대로 본문에 반영된다.</t>
         </is>
       </c>
       <c r="H21" s="3"/>
@@ -761,17 +761,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거·schema·날짜 후보가 잘못된 응답을 차단하는지 확인한다.</t>
+          <t xml:space="preserve">동시 수정과 일괄 수정 실패의 원자성을 확인한다.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무근거 인용·깨진 JSON·없는 날짜 ID</t>
+          <t xml:space="preserve">같은 version 요청·정상 1건과 stale 1건</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE로 처리되고 잘못된 결과는 저장되지 않는다.</t>
+          <t xml:space="preserve">오래된 요청은 거부되고 일괄 수정은 전체 롤백된다.</t>
         </is>
       </c>
       <c r="H22" s="3"/>
@@ -788,17 +788,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 변경과 일부 분석 실패 상태를 구분하는지 확인한다.</t>
+          <t xml:space="preserve">검수 완료가 버전 변경과 재청킹 작업으로 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 중 원문 변경·분석기 1개 실패</t>
+          <t xml:space="preserve">수정 완료 문서</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 변경은 중단되고 일부 실패는 PARTIAL로 기록된다.</t>
+          <t xml:space="preserve">text_version이 증가하고 기존 청크가 stale 처리된 뒤 재청킹된다.</t>
         </is>
       </c>
       <c r="H23" s="3"/>
@@ -806,34 +806,26 @@
     </row>
     <row r="24" ht="38" customHeight="1">
       <c r="A24" s="3"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-ANL-02</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항·일정 검토 연동</t>
-        </is>
-      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 후보의 검토 상태 전이를 확인한다.</t>
+          <t xml:space="preserve">재인덱싱 전후 검색 결과가 섞이지 않는지 확인한다.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 결정 4건</t>
+          <t xml:space="preserve">수정 전 문구·수정 후 문구</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인·거절·취소와 결정자·시각이 저장된다.</t>
+          <t xml:space="preserve">낡은 근거는 최신으로 표시되지 않고 새 청크만 검색된다.</t>
         </is>
       </c>
       <c r="H24" s="3"/>
@@ -845,22 +837,22 @@
       <c r="C25" s="4"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일정 후보의 검토 상태 전이를 확인한다.</t>
+          <t xml:space="preserve">A~D 박스를 병합해 신규 E를 만들고 재조회한 뒤 병합 되돌리기를 확인한다.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 일정 4건</t>
+          <t xml:space="preserve">서로 다른 좌표·텍스트·version의 A~D</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 검토 상태와 수정값이 저장된다.</t>
+          <t xml:space="preserve">E의 영역이 A~D 전체를 포함하고 재조회 후 유지되며, 병합 되돌리기 시 E가 제거되고 A~D가 원상복구된다.</t>
         </is>
       </c>
       <c r="H25" s="3"/>
@@ -872,22 +864,22 @@
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 완료 상태만 하류 기능에 반영되는지 확인한다.</t>
+          <t xml:space="preserve">병합할 수 없는 OCR 요소 요청을 전체 거부하는지 확인한다.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED</t>
+          <t xml:space="preserve">다른 page/version·중복 ID·삭제/제외 요소</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인 항목만 대장과 산출물에 포함된다.</t>
+          <t xml:space="preserve">409 또는 422로 거부되고 원본 요소와 본문은 바뀌지 않는다.</t>
         </is>
       </c>
       <c r="H26" s="3"/>
@@ -895,34 +887,26 @@
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="A27" s="3"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-TSK-01</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">액션 아이템·태스크 연동</t>
-        </is>
-      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상 문서에서 원문 근거가 있는 액션 후보만 생성하는지 확인한다.</t>
+          <t xml:space="preserve">OCR 일괄 변경 요청의 입력 경계와 원자성을 확인한다.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서·회의록·후보 없는 문서</t>
+          <t xml:space="preserve">부분 변경·빈 변경·중복 ID·잘못된 좌표·요청 상한</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상 계약의 근거 후보만 생성되고 후보가 없으면 모델을 호출하지 않는다.</t>
+          <t xml:space="preserve">유효한 부분 변경만 허용되고 잘못된 항목이 있으면 전체 요청이 거부된다.</t>
         </is>
       </c>
       <c r="H27" s="3"/>
@@ -930,26 +914,34 @@
     </row>
     <row r="28" ht="38" customHeight="1">
       <c r="A28" s="3"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-ANL-01</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 요약·분류·분석 상태 연동</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석 시 미검토 후보만 교체하는지 확인한다.</t>
+          <t xml:space="preserve">요약·분류·일정 분석 결과가 저장되는지 확인한다.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING·APPROVED 후보</t>
+          <t xml:space="preserve">요약·유형·날짜가 있는 문서</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING만 교체되고 검토 완료 이력은 유지된다.</t>
+          <t xml:space="preserve">분석별 구조화 결과와 근거가 저장된다.</t>
         </is>
       </c>
       <c r="H28" s="3"/>
@@ -961,22 +953,22 @@
       <c r="C29" s="4"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">후보 승인·거절이 태스크 보드에 맞게 반영되는지 확인한다.</t>
+          <t xml:space="preserve">근거·schema·날짜 후보가 잘못된 응답을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안 2건</t>
+          <t xml:space="preserve">무근거 인용·깨진 JSON·없는 날짜 ID</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 항목은 태스크 1건이 되고 거절 항목은 보드에 나타나지 않는다.</t>
+          <t xml:space="preserve">AI_INVALID_RESPONSE로 처리되고 잘못된 결과는 저장되지 않는다.</t>
         </is>
       </c>
       <c r="H29" s="3"/>
@@ -984,34 +976,26 @@
     </row>
     <row r="30" ht="38" customHeight="1">
       <c r="A30" s="3"/>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-AMT-01</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 추출·검증·재분석 연동</t>
-        </is>
-      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 금액 응답을 PENDING 항목으로 저장하는지 확인한다.</t>
+          <t xml:space="preserve">원문 변경과 일부 분석 실패 상태를 구분하는지 확인한다.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문자열 숫자가 포함된 정상 JSON</t>
+          <t xml:space="preserve">분석 중 원문 변경·분석기 1개 실패</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">숫자가 정규화되고 source revision과 함께 저장된다.</t>
+          <t xml:space="preserve">원문 변경은 중단되고 일부 실패는 PARTIAL로 기록된다.</t>
         </is>
       </c>
       <c r="H30" s="3"/>
@@ -1023,22 +1007,22 @@
       <c r="C31" s="4"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비표준·미지원 금액 응답을 차단하는지 확인한다.</t>
+          <t xml:space="preserve">긴 문서를 구간별 근거 추출·선택·최종 요약 순서로 처리하는지 확인한다.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">코드펜스·잘못된 root·NaN·unknown·음수</t>
+          <t xml:space="preserve">입력 한도 초과 문서·FACTS·SELECT·FINAL</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE이며 금액 항목이 저장되지 않는다.</t>
+          <t xml:space="preserve">문서 끝까지 처리하고 검증된 원문 근거만 최종 요약에 사용한다.</t>
         </is>
       </c>
       <c r="H31" s="3"/>
@@ -1050,22 +1034,22 @@
       <c r="C32" s="4"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석 시 미검토 금액만 교체하는지 확인한다.</t>
+          <t xml:space="preserve">긴 문서의 근거와 구간 경계를 잘못 만든 응답을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING·APPROVED 혼합</t>
+          <t xml:space="preserve">허구 인용·없는 근거 ID·구간 상한 초과</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING만 교체되고 검토 이력은 보존된다.</t>
+          <t xml:space="preserve">잘못된 근거는 저장되지 않고 문서 꼬리를 버리지 않은 채 명확한 오류로 종료된다.</t>
         </is>
       </c>
       <c r="H32" s="3"/>
@@ -1073,34 +1057,26 @@
     </row>
     <row r="33" ht="38" customHeight="1">
       <c r="A33" s="3"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-AMT-02</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 계산·검토·집계 연동</t>
-        </is>
-      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량·단가·VAT와 기재 금액을 검산하는지 확인한다.</t>
+          <t xml:space="preserve">분석기 하나의 예상 가능한 실패를 나머지 분석기와 격리하는지 확인한다.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">공급가액·VAT·불일치 금액</t>
+          <t xml:space="preserve">성공 분석기·AI_INVALID_RESPONSE 분석기</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAT 제외 합계와 불일치가 표시되고 원값은 유지된다.</t>
+          <t xml:space="preserve">성공 결과는 저장되고 작업은 PARTIAL이며 실패 분석기와 오류 코드가 기록된다.</t>
         </is>
       </c>
       <c r="H33" s="3"/>
@@ -1112,22 +1088,22 @@
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">혼합 통화와 계산 경계를 차단하는지 확인한다.</t>
+          <t xml:space="preserve">분석 실행 메타데이터가 모든 결과 저장 경로에 남는지 확인한다.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KRW·USD 혼합 문서</t>
+          <t xml:space="preserve">일반·금액·결정/일정·태스크 제안 분석</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">통화가 섞인 집계는 오류로 처리된다.</t>
+          <t xml:space="preserve">provider·model_name·prompt_version·tokens·latency_ms와 원문 revision이 함께 기록된다.</t>
         </is>
       </c>
       <c r="H34" s="3"/>
@@ -1135,26 +1111,34 @@
     </row>
     <row r="35" ht="38" customHeight="1">
       <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-ANL-02</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항·일정 검토 연동</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 검토 상태와 권한이 집계에 반영되는지 확인한다.</t>
+          <t xml:space="preserve">결정 후보의 검토 상태 전이를 확인한다.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED·VIEWER</t>
+          <t xml:space="preserve">PENDING 결정 4건</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인만 집계되고 VIEWER의 제한 경로는 차단된다.</t>
+          <t xml:space="preserve">승인·수정 승인·거절·취소와 결정자·시각이 저장된다.</t>
         </is>
       </c>
       <c r="H35" s="3"/>
@@ -1166,22 +1150,22 @@
       <c r="C36" s="4"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석 유효 snapshot을 원자적으로 전환하는지 확인한다.</t>
+          <t xml:space="preserve">일정 후보의 검토 상태 전이를 확인한다.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이전 완료 분석·신규 일부/전체 검토</t>
+          <t xml:space="preserve">PENDING 일정 4건</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">부분 검토 중 기존 합계를 유지하고 완료 후 새 snapshot으로 전환된다.</t>
+          <t xml:space="preserve">각 검토 상태와 수정값이 저장된다.</t>
         </is>
       </c>
       <c r="H36" s="3"/>
@@ -1189,34 +1173,26 @@
     </row>
     <row r="37" ht="38" customHeight="1">
       <c r="A37" s="3"/>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-SRH-01</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 조회·하이브리드 검색 연동</t>
-        </is>
-      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 목록 페이징과 필터 상태가 일치하는지 확인한다.</t>
+          <t xml:space="preserve">검토 완료 상태만 하류 기능에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 21건·size 20·유형 필터</t>
+          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">페이지 건수와 URL 상태가 맞고 필터 변경 시 첫 페이지로 이동한다.</t>
+          <t xml:space="preserve">승인·수정 승인 항목만 대장과 산출물에 포함된다.</t>
         </is>
       </c>
       <c r="H37" s="3"/>
@@ -1224,26 +1200,34 @@
     </row>
     <row r="38" ht="38" customHeight="1">
       <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-TSK-01</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액션 아이템·태스크 연동</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문단과 표 구조를 유지해 검색 청크를 만드는지 확인한다.</t>
+          <t xml:space="preserve">대상 문서에서 원문 근거가 있는 액션 후보만 생성하는지 확인한다.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문단·표 구조 요소</t>
+          <t xml:space="preserve">계약서·회의록·후보 없는 문서</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">표 행이 깨지지 않고 구조 경계가 유지된다.</t>
+          <t xml:space="preserve">대상 계약의 근거 후보만 생성되고 후보가 없으면 모델을 호출하지 않는다.</t>
         </is>
       </c>
       <c r="H38" s="3"/>
@@ -1255,22 +1239,22 @@
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">벡터·키워드 검색과 재순위가 연결되는지 확인한다.</t>
+          <t xml:space="preserve">재분석 시 미검토 후보만 교체하는지 확인한다.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">키워드·의미 혼합 질의</t>
+          <t xml:space="preserve">PENDING·APPROVED 후보</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 결과가 융합되고 reranker 순서로 반환된다.</t>
+          <t xml:space="preserve">PENDING만 교체되고 검토 완료 이력은 유지된다.</t>
         </is>
       </c>
       <c r="H39" s="3"/>
@@ -1282,22 +1266,22 @@
       <c r="C40" s="4"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 경계와 장애 fallback을 확인한다.</t>
+          <t xml:space="preserve">후보 승인·거절이 태스크 보드에 맞게 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">%·_ 검색어·reranker 오류·평가 질의</t>
+          <t xml:space="preserve">PENDING 제안 2건</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">와일드카드는 escape되고 장애 시 융합 순서로 결과를 반환한다.</t>
+          <t xml:space="preserve">승인 항목은 태스크 1건이 되고 거절 항목은 보드에 나타나지 않는다.</t>
         </is>
       </c>
       <c r="H40" s="3"/>
@@ -1305,34 +1289,26 @@
     </row>
     <row r="41" ht="38" customHeight="1">
       <c r="A41" s="3"/>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-CHAT-01</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">근거 제한 질의응답 연동</t>
-        </is>
-      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">예산 안에서 조립한 근거만 답변에 사용하는지 확인한다.</t>
+          <t xml:space="preserve">태스크 권한과 입력값 오류를 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">긴 청크 다건·budget 4000</t>
+          <t xml:space="preserve">VIEWER CRUD·빈/공백 제목·비멤버 담당자·과거 마감일</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">예산을 넘지 않고 조립된 evidence만 인용한다.</t>
+          <t xml:space="preserve">VIEWER 쓰기는 403이고 잘못된 값은 계약 오류로 차단되며 태스크·활동 행이 남지 않는다.</t>
         </is>
       </c>
       <c r="H41" s="3"/>
@@ -1344,22 +1320,22 @@
       <c r="C42" s="4"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과가 없을 때 모델 호출을 생략하는지 확인한다.</t>
+          <t xml:space="preserve">태스크 상태와 활동 기록이 함께 변경되는지 확인한다.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과 0건</t>
+          <t xml:space="preserve">생성·수정·DONE 전환·재개·삭제</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 없음으로 응답하고 모델을 호출하지 않는다.</t>
+          <t xml:space="preserve">DONE 진입 시 completed_at이 생기고 이탈 시 제거되며 actor·details와 삭제된 task_title이 남는다.</t>
         </is>
       </c>
       <c r="H42" s="3"/>
@@ -1371,22 +1347,22 @@
       <c r="C43" s="4"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용 범위 밖 근거를 가진 답변을 차단하는지 확인한다.</t>
+          <t xml:space="preserve">보드 변경 후 대시보드 집계가 갱신되는지 확인한다.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">조립하지 않은 evidence ID</t>
+          <t xml:space="preserve">태스크 생성·상태 변경·삭제</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잘못된 답변은 저장·표시되지 않고 보류 응답을 반환한다.</t>
+          <t xml:space="preserve">별도 강제 새로고침 없이 열린 태스크 수와 최근 활동이 최신 서버 값으로 표시된다.</t>
         </is>
       </c>
       <c r="H43" s="3"/>
@@ -1396,12 +1372,12 @@
       <c r="A44" s="3"/>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-LAB-01</t>
+          <t xml:space="preserve">IT-AMT-01</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인원·기간·투입률 인건비 계산 연동</t>
+          <t xml:space="preserve">금액 추출·검증·재분석 연동</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1411,17 +1387,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명시 인월과 기술자별 인월을 계산하는지 확인한다.</t>
+          <t xml:space="preserve">정상 금액 응답을 PENDING 항목으로 저장하는지 확인한다.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9,500,000원×6인월·기술자 2명</t>
+          <t xml:space="preserve">문자열 숫자가 포함된 정상 JSON</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 단가와 인월에 맞는 금액과 근거가 반환된다.</t>
+          <t xml:space="preserve">숫자가 정규화되고 source revision과 함께 저장된다.</t>
         </is>
       </c>
       <c r="H44" s="3"/>
@@ -1438,17 +1414,17 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인원·개월·투입률을 유효 인월로 계산하는지 확인한다.</t>
+          <t xml:space="preserve">비표준·미지원 금액 응답을 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
+          <t xml:space="preserve">코드펜스·잘못된 root·NaN·unknown·음수</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 3인월과 28,500,000원이 반환된다.</t>
+          <t xml:space="preserve">AI_INVALID_RESPONSE이며 금액 항목이 저장되지 않는다.</t>
         </is>
       </c>
       <c r="H45" s="3"/>
@@ -1465,17 +1441,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모호한 매핑과 투입률 경계를 임의 계산하지 않는지 확인한다.</t>
+          <t xml:space="preserve">재분석 시 미검토 금액만 교체하는지 확인한다.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이름 매핑 없음·0%·100%·120%·1.5인월</t>
+          <t xml:space="preserve">PENDING·APPROVED 혼합</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 범위만 계산하고 모호한 경우 명확화를 요청한다.</t>
+          <t xml:space="preserve">PENDING만 교체되고 검토 이력은 보존된다.</t>
         </is>
       </c>
       <c r="H46" s="3"/>
@@ -1485,12 +1461,12 @@
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-DLV-01</t>
+          <t xml:space="preserve">IT-AMT-02</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드 연동</t>
+          <t xml:space="preserve">금액 계산·검토·집계 연동</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -1500,17 +1476,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 DB 자료로 프로젝트 현황 미리보기를 만드는지 확인한다.</t>
+          <t xml:space="preserve">수량·단가·VAT와 기재 금액을 검산하는지 확인한다.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROJECT_STATUS·프로젝트·태스크·일정</t>
+          <t xml:space="preserve">공급가액·VAT·불일치 금액</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기간 없이 다섯 절과 현재 자료 표가 생성된다.</t>
+          <t xml:space="preserve">VAT 제외 합계와 불일치가 표시되고 원값은 유지된다.</t>
         </is>
       </c>
       <c r="H47" s="3"/>
@@ -1527,17 +1503,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출력 형식별 내용과 데이터형이 일치하는지 확인한다.</t>
+          <t xml:space="preserve">혼합 통화와 계산 경계를 차단하는지 확인한다.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MD·HTML·XLSX·PDF</t>
+          <t xml:space="preserve">KRW·USD 혼합 문서</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">절과 자료가 같고 XLSX 금액은 숫자 셀로 생성된다.</t>
+          <t xml:space="preserve">통화가 섞인 집계는 오류로 처리된다.</t>
         </is>
       </c>
       <c r="H48" s="3"/>
@@ -1554,17 +1530,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원천 자료 변경과 미리보기 건수 규칙을 확인한다.</t>
+          <t xml:space="preserve">금액 검토 상태와 권한이 집계에 반영되는지 확인한다.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성 후 자료 추가·재분석 금액</t>
+          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED·VIEWER</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stale가 표시되고 count와 본문이 같은 유효 snapshot을 사용한다.</t>
+          <t xml:space="preserve">승인·수정 승인만 집계되고 VIEWER의 제한 경로는 차단된다.</t>
         </is>
       </c>
       <c r="H49" s="3"/>
@@ -1581,17 +1557,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드를 확인한다.</t>
+          <t xml:space="preserve">재분석 유효 snapshot을 원자적으로 전환하는지 확인한다.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">네 출력 형식·생성된 산출물 ID</t>
+          <t xml:space="preserve">이전 완료 분석·신규 일부/전체 검토</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">네 파일이 이력에 남고 제목 기반 파일명으로 다시 다운로드된다.</t>
+          <t xml:space="preserve">부분 검토 중 기존 합계를 유지하고 완료 후 새 snapshot으로 전환된다.</t>
         </is>
       </c>
       <c r="H50" s="3"/>
@@ -1601,12 +1577,12 @@
       <c r="A51" s="3"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT-SYS-01</t>
+          <t xml:space="preserve">IT-SRH-01</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오류 응답·request_id·worker 복구 연동</t>
+          <t xml:space="preserve">문서 조회·하이브리드 검색 연동</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -1616,17 +1592,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">API 오류 응답 형식과 request_id를 확인한다.</t>
+          <t xml:space="preserve">문서 목록 페이징과 필터 상태가 일치하는지 확인한다.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404·405·409·422·middleware 없는 요청</t>
+          <t xml:space="preserve">문서 21건·size 20·유형 필터</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">code·message·request_id가 같은 구조로 반환된다.</t>
+          <t xml:space="preserve">페이지 건수와 URL 상태가 맞고 필터 변경 시 첫 페이지로 이동한다.</t>
         </is>
       </c>
       <c r="H51" s="3"/>
@@ -1643,17 +1619,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">request_id가 API에서 worker 로그까지 전달되는지 확인한다.</t>
+          <t xml:space="preserve">문단과 표 구조를 유지해 검색 청크를 만드는지 확인한다.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고정 X-Request-ID 재처리 요청</t>
+          <t xml:space="preserve">문단·표 구조 요소</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">API·queue·worker 로그에 같은 ID가 기록된다.</t>
+          <t xml:space="preserve">표 행이 깨지지 않고 구조 경계가 유지된다.</t>
         </is>
       </c>
       <c r="H52" s="3"/>
@@ -1670,17 +1646,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker와 AI 공급자 장애를 구분해 복구하는지 확인한다.</t>
+          <t xml:space="preserve">벡터·키워드 검색과 재순위가 연결되는지 확인한다.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker 중단·Ollama 연결 실패·schema 오류</t>
+          <t xml:space="preserve">키워드·의미 혼합 질의</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업은 유실되지 않고 provider와 응답 형식 오류가 구분된다.</t>
+          <t xml:space="preserve">두 결과가 융합되고 reranker 순서로 반환된다.</t>
         </is>
       </c>
       <c r="H53" s="3"/>
@@ -1688,34 +1664,26 @@
     </row>
     <row r="54" ht="38" customHeight="1">
       <c r="A54" s="3"/>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IT-ISO-01</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 데이터 격리 연동</t>
-        </is>
-      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 프로젝트 리소스에 접근할 수 없는지 확인한다.</t>
+          <t xml:space="preserve">검색 경계와 장애 fallback을 확인한다.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타 프로젝트 문서·OCR·분석·금액·검색·산출물 ID</t>
+          <t xml:space="preserve">%·_ 검색어·reranker 오류·평가 질의</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 경로가 404이며 데이터가 노출되지 않는다.</t>
+          <t xml:space="preserve">와일드카드는 escape되고 장애 시 융합 순서로 결과를 반환한다.</t>
         </is>
       </c>
       <c r="H54" s="3"/>
@@ -1723,26 +1691,34 @@
     </row>
     <row r="55" ht="38" customHeight="1">
       <c r="A55" s="3"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-CHAT-01</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 제한 질의응답 연동</t>
+        </is>
+      </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중복 파일 검사가 프로젝트 안에서만 적용되는지 확인한다.</t>
+          <t xml:space="preserve">예산 안에서 조립한 근거만 답변에 사용하는지 확인한다.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 hash·프로젝트 2개</t>
+          <t xml:space="preserve">긴 청크 다건·budget 4000</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 프로젝트에는 한 번씩 업로드할 수 있다.</t>
+          <t xml:space="preserve">예산을 넘지 않고 조립된 evidence만 인용한다.</t>
         </is>
       </c>
       <c r="H55" s="3"/>
@@ -1754,63 +1730,502 @@
       <c r="C56" s="4"/>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멤버 제외 직후 기존 세션 접근을 차단하는지 확인한다.</t>
+          <t xml:space="preserve">검색 결과가 없을 때 모델 호출을 생략하는지 확인한다.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제외 전 로그인 세션·열린 화면</t>
+          <t xml:space="preserve">검색 결과 0건</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존 토큰과 화면에서도 프로젝트 접근이 즉시 차단된다.</t>
+          <t xml:space="preserve">근거 없음으로 응답하고 모델을 호출하지 않는다.</t>
         </is>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="2"/>
     </row>
+    <row r="57" ht="38" customHeight="1">
+      <c r="A57" s="3"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">허용 범위 밖 근거를 가진 답변을 차단하는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조립하지 않은 evidence ID</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잘못된 답변은 저장·표시되지 않고 보류 응답을 반환한다.</t>
+        </is>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" ht="38" customHeight="1">
+      <c r="A58" s="3"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-LAB-01</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인원·기간·투입률 인건비 계산 연동</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명시 인월과 기술자별 인월을 계산하는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,500,000원×6인월·기술자 2명</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각 단가와 인월에 맞는 금액과 근거가 반환된다.</t>
+        </is>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" ht="38" customHeight="1">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인원·개월·투입률을 유효 인월로 계산하는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유효 3인월과 28,500,000원이 반환된다.</t>
+        </is>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" ht="38" customHeight="1">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모호한 매핑과 투입률 경계를 임의 계산하지 않는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이름 매핑 없음·0%·100%·120%·1.5인월</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유효 범위만 계산하고 모호한 경우 명확화를 요청한다.</t>
+        </is>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" ht="38" customHeight="1">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-DLV-01</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드 연동</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 DB 자료로 프로젝트 현황 미리보기를 만드는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROJECT_STATUS·프로젝트·태스크·일정</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기간 없이 다섯 절과 현재 자료 표가 생성된다.</t>
+        </is>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" ht="38" customHeight="1">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출력 형식별 내용과 데이터형이 일치하는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MD·HTML·XLSX·PDF</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절과 자료가 같고 XLSX 금액은 숫자 셀로 생성된다.</t>
+        </is>
+      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" ht="38" customHeight="1">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원천 자료 변경과 미리보기 건수 규칙을 확인한다.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 후 자료 추가·재분석 금액</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stale가 표시되고 count와 본문이 같은 유효 snapshot을 사용한다.</t>
+        </is>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" ht="38" customHeight="1">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드를 확인한다.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네 출력 형식·생성된 산출물 ID</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네 파일이 이력에 남고 제목 기반 파일명으로 다시 다운로드된다.</t>
+        </is>
+      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" ht="38" customHeight="1">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-SYS-01</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오류 응답·request_id·worker 복구 연동</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 오류 응답 형식과 request_id를 확인한다.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">404·405·409·422·middleware 없는 요청</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">code·message·request_id가 같은 구조로 반환된다.</t>
+        </is>
+      </c>
+      <c r="H65" s="3"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" ht="38" customHeight="1">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request_id가 API에서 worker 로그까지 전달되는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고정 X-Request-ID 재처리 요청</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API·queue·worker 로그에 같은 ID가 기록된다.</t>
+        </is>
+      </c>
+      <c r="H66" s="3"/>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" ht="38" customHeight="1">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worker와 AI 공급자 장애를 구분해 복구하는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worker 중단·Ollama 연결 실패·schema 오류</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업은 유실되지 않고 provider와 응답 형식 오류가 구분된다.</t>
+        </is>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" ht="38" customHeight="1">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FastAPI 앱과 전체 라우터가 import 오류 없이 시작되는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서비스·스키마·필수 Python 의존성</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내장 타입 이름 충돌과 패키지 누락 없이 API 시작 smoke test가 통과한다.</t>
+        </is>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" ht="38" customHeight="1">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IT-ISO-01</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 데이터 격리 연동</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다른 프로젝트 리소스에 접근할 수 없는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타 프로젝트 문서·OCR·분석·금액·검색·산출물 ID</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모든 경로가 404이며 데이터가 노출되지 않는다.</t>
+        </is>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" ht="38" customHeight="1">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중복 파일 검사가 프로젝트 안에서만 적용되는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같은 hash·프로젝트 2개</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각 프로젝트에는 한 번씩 업로드할 수 있다.</t>
+        </is>
+      </c>
+      <c r="H70" s="3"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" ht="38" customHeight="1">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멤버 제외 직후 기존 세션 접근을 차단하는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제외 전 로그인 세션·열린 화면</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존 토큰과 화면에서도 프로젝트 접근이 즉시 차단된다.</t>
+        </is>
+      </c>
+      <c r="H71" s="3"/>
+      <c r="I71" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="B28:B34"/>
+    <mergeCell ref="C28:C34"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="C38:C43"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="B47:B50"/>
     <mergeCell ref="C47:C50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="C69:C71"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
